--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>118159148</v>
       </c>
       <c r="B15" t="n">
-        <v>90163</v>
+        <v>90173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>118159148</v>
       </c>
       <c r="B15" t="n">
-        <v>90173</v>
+        <v>90185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>118159148</v>
       </c>
       <c r="B15" t="n">
-        <v>90185</v>
+        <v>90186</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>118159148</v>
       </c>
       <c r="B15" t="n">
-        <v>90186</v>
+        <v>90189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>118159148</v>
       </c>
       <c r="B15" t="n">
-        <v>90189</v>
+        <v>90195</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>118159148</v>
       </c>
       <c r="B15" t="n">
-        <v>90195</v>
+        <v>90196</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>118159148</v>
       </c>
       <c r="B15" t="n">
-        <v>90196</v>
+        <v>90203</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,6 +2329,107 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127424384</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90803</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>720</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ebbegärde, Böleskogarna, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>573927</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6303184</v>
+      </c>
+      <c r="S16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Anderstedt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Anderstedt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2334,7 +2334,7 @@
         <v>127424384</v>
       </c>
       <c r="B16" t="n">
-        <v>90803</v>
+        <v>90807</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2430,6 +2430,107 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127683250</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90519</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4823</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hasselsopp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leccinellum pseudoscabrum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Kallenb.) Mikšík</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ebbrgärde, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>573902</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6303243</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Anderstedt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Anderstedt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2334,7 +2334,7 @@
         <v>127424384</v>
       </c>
       <c r="B16" t="n">
-        <v>90807</v>
+        <v>90809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127683250</v>
       </c>
       <c r="B17" t="n">
-        <v>90519</v>
+        <v>90521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2334,7 +2334,7 @@
         <v>127424384</v>
       </c>
       <c r="B16" t="n">
-        <v>90809</v>
+        <v>90815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127683250</v>
       </c>
       <c r="B17" t="n">
-        <v>90521</v>
+        <v>90527</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2334,7 +2334,7 @@
         <v>127424384</v>
       </c>
       <c r="B16" t="n">
-        <v>90815</v>
+        <v>90818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127683250</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>90530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2334,7 +2334,7 @@
         <v>127424384</v>
       </c>
       <c r="B16" t="n">
-        <v>90818</v>
+        <v>90826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127683250</v>
       </c>
       <c r="B17" t="n">
-        <v>90530</v>
+        <v>90538</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2334,7 +2334,7 @@
         <v>127424384</v>
       </c>
       <c r="B16" t="n">
-        <v>90826</v>
+        <v>90827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127683250</v>
       </c>
       <c r="B17" t="n">
-        <v>90538</v>
+        <v>90539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2334,7 +2334,7 @@
         <v>127424384</v>
       </c>
       <c r="B16" t="n">
-        <v>90827</v>
+        <v>90828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127683250</v>
       </c>
       <c r="B17" t="n">
-        <v>90539</v>
+        <v>90540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2334,7 +2334,7 @@
         <v>127424384</v>
       </c>
       <c r="B16" t="n">
-        <v>90828</v>
+        <v>90829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127683250</v>
       </c>
       <c r="B17" t="n">
-        <v>90540</v>
+        <v>90541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2531,6 +2531,209 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128347842</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97437</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222593</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Safsa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Osmunda regalis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Snärjebäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>573896</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6303180</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128347699</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92679</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Snärjebäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>573884</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6303241</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2435,7 +2435,7 @@
         <v>127683250</v>
       </c>
       <c r="B17" t="n">
-        <v>90541</v>
+        <v>90547</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>128347842</v>
       </c>
       <c r="B18" t="n">
-        <v>97437</v>
+        <v>97442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2536,7 +2536,7 @@
         <v>128347842</v>
       </c>
       <c r="B18" t="n">
-        <v>97442</v>
+        <v>97535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2536,7 +2536,7 @@
         <v>128347842</v>
       </c>
       <c r="B18" t="n">
-        <v>97535</v>
+        <v>97547</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2536,7 +2536,7 @@
         <v>128347842</v>
       </c>
       <c r="B18" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2536,7 +2536,7 @@
         <v>128347842</v>
       </c>
       <c r="B18" t="n">
-        <v>97549</v>
+        <v>97550</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2536,7 +2536,7 @@
         <v>128347842</v>
       </c>
       <c r="B18" t="n">
-        <v>97550</v>
+        <v>97577</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2536,7 +2536,7 @@
         <v>128347842</v>
       </c>
       <c r="B18" t="n">
-        <v>97577</v>
+        <v>97590</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2536,7 +2536,7 @@
         <v>128347842</v>
       </c>
       <c r="B18" t="n">
-        <v>97590</v>
+        <v>97594</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>92834</v>
+        <v>93216</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -2638,7 +2638,7 @@
         <v>128347699</v>
       </c>
       <c r="B19" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72810173</v>
+        <v>232150</v>
       </c>
       <c r="B2" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2008</v>
+        <v>720</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,20 +713,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Snärjebäcken uppströms Ebbetorp, Sm</t>
+          <t>Ebbegärde, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573665.4821134708</v>
+        <v>573928</v>
       </c>
       <c r="R2" t="n">
-        <v>6303365.575447014</v>
+        <v>6303247</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Snärjebäcken bildar här en kvill i vilken det växer gran, blandat med ek, björk, ask och al och en stor andel gammal idegran.</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,84 +763,74 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Aron Edman</t>
+          <t>Tomas Anderstedt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Aron Edman</t>
+          <t>Tomas Anderstedt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78707597</v>
+        <v>118159148</v>
       </c>
       <c r="B3" t="n">
-        <v>95613</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222593</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Osmunda regalis</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ebbegärde, Böleskogarna, Sm</t>
+          <t>Ebbegärde, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573926.6984567335</v>
+        <v>573934</v>
       </c>
       <c r="R3" t="n">
-        <v>6303183.783566988</v>
+        <v>6303193</v>
       </c>
       <c r="S3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,62 +887,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111782566</v>
+        <v>127424384</v>
       </c>
       <c r="B4" t="n">
-        <v>103369</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>720</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ebbegärde, Sm</t>
+          <t>Ebbegärde, Böleskogarna, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573877</v>
+        <v>573927</v>
       </c>
       <c r="R4" t="n">
-        <v>6303234</v>
+        <v>6303184</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,12 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,80 +969,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Tomas Anderstedt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Tomas Anderstedt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111782565</v>
+        <v>95935888</v>
       </c>
       <c r="B5" t="n">
-        <v>100532</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223246</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ebbegärde, Sm</t>
+          <t>V Ebbegärde, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573877</v>
+        <v>573986</v>
       </c>
       <c r="R5" t="n">
-        <v>6303226</v>
+        <v>6303215</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-09-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-09-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,77 +1070,74 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111782567</v>
+        <v>112507258</v>
       </c>
       <c r="B6" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87237</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1980</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Porslinsblå spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius cumatilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ebbegärde, Sm</t>
+          <t>Snärjebäcken kalkbarrskog, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573909</v>
+        <v>573889</v>
       </c>
       <c r="R6" t="n">
-        <v>6303235</v>
+        <v>6303251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,12 +1164,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kalkrik blandskog utmed Snärjebäcken. Blåsippor hassel idegran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,54 +1189,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Aron Edman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Aron Edman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112507258</v>
+        <v>72810173</v>
       </c>
       <c r="B7" t="n">
-        <v>85423</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1980</v>
+        <v>2008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porslinsblå spindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius cumatilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,17 +1242,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Snärjebäcken kalkbarrskog, Sm</t>
+          <t>Snärjebäcken uppströms Ebbetorp, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573889</v>
+        <v>573665</v>
       </c>
       <c r="R7" t="n">
-        <v>6303251</v>
+        <v>6303366</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,17 +1276,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Kalkrik blandskog utmed Snärjebäcken. Blåsippor hassel idegran.</t>
+          <t>Snärjebäcken bildar här en kvill i vilken det växer gran, blandat med ek, björk, ask och al och en stor andel gammal idegran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,6 +1295,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1378,15 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113591316</v>
+        <v>127683250</v>
       </c>
       <c r="B8" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,51 +1325,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>4823</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselsopp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leccinellum pseudoscabrum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Kallenb.) Mikšík</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ebbegärde, Snärjebäcken, Sm</t>
+          <t>Ebbrgärde, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573988</v>
+        <v>573902</v>
       </c>
       <c r="R8" t="n">
-        <v>6303165</v>
+        <v>6303243</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,12 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,90 +1396,70 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog, basisk</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Tomas Anderstedt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Tomas Anderstedt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113591323</v>
+        <v>128347699</v>
       </c>
       <c r="B9" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ebbegärde, Snärjebäcken, Sm</t>
+          <t>Snärjebäcken, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573927</v>
+        <v>573884</v>
       </c>
       <c r="R9" t="n">
-        <v>6303162</v>
+        <v>6303241</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,12 +1483,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,38 +1497,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrblandskog, basisk</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113591325</v>
+        <v>113591319</v>
       </c>
       <c r="B10" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1660,7 +1551,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1674,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573937</v>
+        <v>573975</v>
       </c>
       <c r="R10" t="n">
-        <v>6303193</v>
+        <v>6303172</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1741,15 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113591326</v>
+        <v>111782566</v>
       </c>
       <c r="B11" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,48 +1643,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221423</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ebbegärde, Snärjebäcken, Sm</t>
+          <t>Ebbegärde, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573951</v>
+        <v>573878</v>
       </c>
       <c r="R11" t="n">
-        <v>6303179</v>
+        <v>6303234</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,12 +1706,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,11 +1722,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog, basisk</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1862,15 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113591318</v>
+        <v>111782567</v>
       </c>
       <c r="B12" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1768,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1905,21 +1776,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ebbegärde, Snärjebäcken, Sm</t>
+          <t>Ebbegärde, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573965</v>
+        <v>573909</v>
       </c>
       <c r="R12" t="n">
-        <v>6303192</v>
+        <v>6303236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,12 +1812,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,11 +1828,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrblandskog, basisk</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1983,15 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113591319</v>
+        <v>113591313</v>
       </c>
       <c r="B13" t="n">
-        <v>109545</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2023,7 +1879,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2037,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573975</v>
+        <v>573960</v>
       </c>
       <c r="R13" t="n">
-        <v>6303172</v>
+        <v>6303151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2104,15 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113591320</v>
+        <v>113591315</v>
       </c>
       <c r="B14" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +1990,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2158,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573975</v>
+        <v>573950</v>
       </c>
       <c r="R14" t="n">
-        <v>6303172</v>
+        <v>6303162</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2225,53 +2076,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118159148</v>
+        <v>113591316</v>
       </c>
       <c r="B15" t="n">
-        <v>90203</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>720</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ebbegärde, Sm</t>
+          <t>Ebbegärde, Snärjebäcken, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573934</v>
+        <v>573988</v>
       </c>
       <c r="R15" t="n">
-        <v>6303193</v>
+        <v>6303165</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2298,12 +2155,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,70 +2169,85 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrblandskog, basisk</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Anderstedt</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Anderstedt</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127424384</v>
+        <v>113591318</v>
       </c>
       <c r="B16" t="n">
-        <v>90829</v>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>720</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ebbegärde, Böleskogarna, Sm</t>
+          <t>Ebbegärde, Snärjebäcken, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573927</v>
+        <v>573965</v>
       </c>
       <c r="R16" t="n">
-        <v>6303184</v>
+        <v>6303192</v>
       </c>
       <c r="S16" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2399,12 +2271,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,29 +2285,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Barrblandskog, basisk</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Anderstedt</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Anderstedt</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127683250</v>
+        <v>113591320</v>
       </c>
       <c r="B17" t="n">
-        <v>90547</v>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,40 +2319,51 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4823</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hasselsopp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leccinellum pseudoscabrum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kallenb.) Mikšík</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ebbrgärde, Sm</t>
+          <t>Ebbegärde, Snärjebäcken, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573902</v>
+        <v>573975</v>
       </c>
       <c r="R17" t="n">
-        <v>6303243</v>
+        <v>6303172</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2500,12 +2387,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,29 +2401,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrblandskog, basisk</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Anderstedt</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Anderstedt</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128347842</v>
+        <v>113591323</v>
       </c>
       <c r="B18" t="n">
-        <v>97594</v>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2544,41 +2435,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222593</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osmunda regalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Snärjebäcken, Sm</t>
+          <t>Ebbegärde, Snärjebäcken, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573896</v>
+        <v>573927</v>
       </c>
       <c r="R18" t="n">
-        <v>6303180</v>
+        <v>6303162</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2602,12 +2503,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,29 +2517,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrblandskog, basisk</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128347699</v>
+        <v>113591325</v>
       </c>
       <c r="B19" t="n">
-        <v>93242</v>
+        <v>101326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,40 +2551,51 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Snärjebäcken, Sm</t>
+          <t>Ebbegärde, Snärjebäcken, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>573884</v>
+        <v>573937</v>
       </c>
       <c r="R19" t="n">
-        <v>6303241</v>
+        <v>6303193</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2703,12 +2619,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2717,22 +2633,460 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrblandskog, basisk</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113591326</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ebbegärde, Snärjebäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>573951</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6303179</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-11-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-11-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrblandskog, basisk</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>78707597</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98072</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222593</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Safsa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Osmunda regalis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ebbegärde, Böleskogarna, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>573927</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6303184</v>
+      </c>
+      <c r="S21" t="n">
+        <v>21</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Anderstedt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Anderstedt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128347842</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98072</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222593</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Safsa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Osmunda regalis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Snärjebäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>573896</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6303180</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Patrik Celander</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Patrik Celander</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>111782565</v>
+      </c>
+      <c r="B23" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ebbegärde, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>573877</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6303226</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45095-2021 artfynd.xlsx
+++ b/artfynd/A 45095-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/232150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118159148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127424384</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95935888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507258</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72810173</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127683250</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347699</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113591319</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1735,6 +1785,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111782566</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1841,6 +1896,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111782567</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113591313</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113591315</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113591316</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2305,6 +2380,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113591318</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2421,6 +2501,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113591320</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2537,6 +2622,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113591323</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2653,6 +2743,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113591325</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2769,6 +2864,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113591326</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2879,6 +2979,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78707597</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2981,6 +3086,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347842</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3087,8 +3197,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111782565</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>